--- a/Claude_ai/Projects/Examples/04_Business_Intelligence/sample_files/星橋科技_2026上半年產品銷售數據.xlsx
+++ b/Claude_ai/Projects/Examples/04_Business_Intelligence/sample_files/星橋科技_2026上半年產品銷售數據.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2026上半年產品銷售" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Q1_銷售明細" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Q2_銷售明細" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="產品利潤與負責團隊" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,10 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-  </numFmts>
-  <fonts count="2">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,10 +28,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Microsoft JhengHei"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -43,8 +47,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
+        <fgColor rgb="001E3A8A"/>
+        <bgColor rgb="001E3A8A"/>
       </patternFill>
     </fill>
   </fills>
@@ -65,7 +69,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,15 +437,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -449,149 +448,366 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>產品線</t>
+          <t>產品編號</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>產品名稱</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>銷售量 (台)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>營收金額 (萬新台幣)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>目標達成率</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1月</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>PROD-AI-01</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>智慧客服系統 2.0 (北極星)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2月</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>PROD-AI-01</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>智慧客服系統 2.0 (北極星)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>3月</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>PROD-AI-01</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>智慧客服系統 2.0 (北極星)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>產品編號</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>產品名稱</t>
+        </is>
+      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>銷售量 (台)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>營收金額 (萬新台幣)</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>目標達成率</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>PROD-AI-01</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>智慧客服系統 2.0 (北極星)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>PROD-AI-01</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>智慧客服系統 2.0 (北極星)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>PROD-AI-01</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>智慧客服系統 2.0 (北極星)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>產品編號</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>產品名稱</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>產品分類</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>毛利率</t>
+        </is>
+      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>目標達成率</t>
+          <t>負責團隊</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>產品負責人</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1月</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PROD-AI-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>智慧客服系統 2.0 (北極星)</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>120</v>
-      </c>
-      <c r="D2" t="n">
-        <v>240</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.96</v>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>企業AI解決方案</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>企業應用組</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>林特助</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2月</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>智慧客服系統 2.0 (北極星)</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>150</v>
-      </c>
-      <c r="D3" t="n">
-        <v>300</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>1</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>PROD-SEC-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>零信任資安過橋中樞</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>資安與法規合規</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>基礎架構組</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>陳資深架構師</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3月</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>智慧客服系統 2.0 (北極星)</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>180</v>
-      </c>
-      <c r="D4" t="n">
-        <v>360</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4月</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>智慧客服系統 2.0 (北極星)</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>210</v>
-      </c>
-      <c r="D5" t="n">
-        <v>420</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5月</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>智慧客服系統 2.0 (北極星)</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>250</v>
-      </c>
-      <c r="D6" t="n">
-        <v>500</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6月</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>智慧客服系統 2.0 (北極星)</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>300</v>
-      </c>
-      <c r="D7" t="n">
-        <v>600</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>1.2</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>PROD-DEV-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>DevOps自動化發布管線</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>開發者效率工具</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>雲端維運組</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>王技術總監</t>
+        </is>
       </c>
     </row>
   </sheetData>
